--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130961918</v>
       </c>
       <c r="B2" t="n">
-        <v>91804</v>
+        <v>91818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>130962101</v>
       </c>
       <c r="B3" t="n">
-        <v>58500</v>
+        <v>58514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B11" t="n">
-        <v>91809</v>
+        <v>91829</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,23 +1660,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R11" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130472</v>
+        <v>131130696</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>91809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1791,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410737</v>
+        <v>410606</v>
       </c>
       <c r="R12" t="n">
-        <v>7037762</v>
+        <v>7037656</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1836,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131131304</v>
+        <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>91829</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,19 +1870,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410603</v>
+        <v>410737</v>
       </c>
       <c r="R13" t="n">
-        <v>7037541</v>
+        <v>7037762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131131304</v>
+        <v>131130696</v>
       </c>
       <c r="B11" t="n">
-        <v>91829</v>
+        <v>91809</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,19 +1660,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410603</v>
+        <v>410606</v>
       </c>
       <c r="R11" t="n">
-        <v>7037541</v>
+        <v>7037656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B12" t="n">
-        <v>91809</v>
+        <v>91829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,23 +1767,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R12" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130961918</v>
       </c>
       <c r="B2" t="n">
-        <v>91829</v>
+        <v>91830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>130962101</v>
       </c>
       <c r="B3" t="n">
-        <v>58520</v>
+        <v>58521</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131130889</v>
       </c>
       <c r="B9" t="n">
-        <v>58520</v>
+        <v>58521</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131129861</v>
       </c>
       <c r="B10" t="n">
-        <v>58520</v>
+        <v>58521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B11" t="n">
-        <v>91809</v>
+        <v>91830</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,23 +1660,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R11" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131131304</v>
+        <v>131130696</v>
       </c>
       <c r="B12" t="n">
-        <v>91829</v>
+        <v>91810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,19 +1763,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410603</v>
+        <v>410606</v>
       </c>
       <c r="R12" t="n">
-        <v>7037541</v>
+        <v>7037656</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2071,6 +2071,109 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131295721</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91830</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>410530</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7037500</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Fabian Pettersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130961918</v>
       </c>
       <c r="B2" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>131131304</v>
       </c>
       <c r="B11" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130696</v>
+        <v>131130472</v>
       </c>
       <c r="B12" t="n">
-        <v>91810</v>
+        <v>57884</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410606</v>
+        <v>410737</v>
       </c>
       <c r="R12" t="n">
-        <v>7037656</v>
+        <v>7037762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131130472</v>
+        <v>131130696</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>91813</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410737</v>
+        <v>410606</v>
       </c>
       <c r="R13" t="n">
-        <v>7037762</v>
+        <v>7037656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,7 +2076,7 @@
         <v>131295721</v>
       </c>
       <c r="B15" t="n">
-        <v>91830</v>
+        <v>91833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1652,7 +1652,7 @@
         <v>131131304</v>
       </c>
       <c r="B11" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1752,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130472</v>
+        <v>131130696</v>
       </c>
       <c r="B12" t="n">
-        <v>57884</v>
+        <v>91814</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410737</v>
+        <v>410606</v>
       </c>
       <c r="R12" t="n">
-        <v>7037762</v>
+        <v>7037656</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131130696</v>
+        <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>91813</v>
+        <v>57884</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410606</v>
+        <v>410737</v>
       </c>
       <c r="R13" t="n">
-        <v>7037656</v>
+        <v>7037762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,7 +2076,7 @@
         <v>131295721</v>
       </c>
       <c r="B15" t="n">
-        <v>91833</v>
+        <v>91834</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>131076706</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131129770</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>131130868</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131130889</v>
       </c>
       <c r="B9" t="n">
-        <v>58521</v>
+        <v>58523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131129861</v>
       </c>
       <c r="B10" t="n">
-        <v>58521</v>
+        <v>58523</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131131304</v>
+        <v>131130696</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91816</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,19 +1660,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410603</v>
+        <v>410606</v>
       </c>
       <c r="R11" t="n">
-        <v>7037541</v>
+        <v>7037656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B12" t="n">
-        <v>91814</v>
+        <v>91836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,23 +1767,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R12" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
         <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>131130718</v>
       </c>
       <c r="B14" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131295721</v>
       </c>
       <c r="B15" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>131076706</v>
       </c>
       <c r="B6" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131129770</v>
       </c>
       <c r="B7" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>131130868</v>
       </c>
       <c r="B8" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131130889</v>
       </c>
       <c r="B9" t="n">
-        <v>58523</v>
+        <v>58524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131129861</v>
       </c>
       <c r="B10" t="n">
-        <v>58523</v>
+        <v>58524</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>131130696</v>
       </c>
       <c r="B11" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>131131304</v>
       </c>
       <c r="B12" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>131130718</v>
       </c>
       <c r="B14" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131295721</v>
       </c>
       <c r="B15" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B11" t="n">
-        <v>91817</v>
+        <v>91837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,23 +1660,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R11" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131131304</v>
+        <v>131130472</v>
       </c>
       <c r="B12" t="n">
-        <v>91837</v>
+        <v>57887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,19 +1763,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410603</v>
+        <v>410737</v>
       </c>
       <c r="R12" t="n">
-        <v>7037541</v>
+        <v>7037762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131130472</v>
+        <v>131130696</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410737</v>
+        <v>410606</v>
       </c>
       <c r="R13" t="n">
-        <v>7037762</v>
+        <v>7037656</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1752,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130472</v>
+        <v>131130696</v>
       </c>
       <c r="B12" t="n">
-        <v>57887</v>
+        <v>91817</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,21 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410737</v>
+        <v>410606</v>
       </c>
       <c r="R12" t="n">
-        <v>7037762</v>
+        <v>7037656</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131130696</v>
+        <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>91817</v>
+        <v>57887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,21 +1870,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410606</v>
+        <v>410737</v>
       </c>
       <c r="R13" t="n">
-        <v>7037656</v>
+        <v>7037762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1107,7 +1107,7 @@
         <v>131076706</v>
       </c>
       <c r="B6" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1214,7 +1214,7 @@
         <v>131129770</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>131130868</v>
       </c>
       <c r="B8" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131130889</v>
       </c>
       <c r="B9" t="n">
-        <v>58524</v>
+        <v>58525</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131129861</v>
       </c>
       <c r="B10" t="n">
-        <v>58524</v>
+        <v>58525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131131304</v>
+        <v>131130696</v>
       </c>
       <c r="B11" t="n">
-        <v>91837</v>
+        <v>91818</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,19 +1660,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410603</v>
+        <v>410606</v>
       </c>
       <c r="R11" t="n">
-        <v>7037541</v>
+        <v>7037656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B12" t="n">
-        <v>91817</v>
+        <v>91838</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,23 +1767,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R12" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
         <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>131130718</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131295721</v>
       </c>
       <c r="B15" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1756,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131131304</v>
+        <v>131130472</v>
       </c>
       <c r="B12" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,19 +1767,23 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1791,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410603</v>
+        <v>410737</v>
       </c>
       <c r="R12" t="n">
-        <v>7037541</v>
+        <v>7037762</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1826,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1836,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,10 +1863,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131130472</v>
+        <v>131131304</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>91838</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1870,23 +1874,19 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410737</v>
+        <v>410603</v>
       </c>
       <c r="R13" t="n">
-        <v>7037762</v>
+        <v>7037541</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B11" t="n">
-        <v>91818</v>
+        <v>91838</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,23 +1660,19 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R11" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1719,7 +1715,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1729,7 +1725,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1756,10 +1752,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130472</v>
+        <v>131130696</v>
       </c>
       <c r="B12" t="n">
-        <v>57888</v>
+        <v>91818</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1767,21 +1763,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1791,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410737</v>
+        <v>410606</v>
       </c>
       <c r="R12" t="n">
-        <v>7037762</v>
+        <v>7037656</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1826,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1836,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1863,10 +1859,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131131304</v>
+        <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>91838</v>
+        <v>57888</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1874,19 +1870,23 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410603</v>
+        <v>410737</v>
       </c>
       <c r="R13" t="n">
-        <v>7037541</v>
+        <v>7037762</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>131129770</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>131130868</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131130889</v>
       </c>
       <c r="B9" t="n">
-        <v>58525</v>
+        <v>58528</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131129861</v>
       </c>
       <c r="B10" t="n">
-        <v>58525</v>
+        <v>58528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1652,7 +1652,7 @@
         <v>131131304</v>
       </c>
       <c r="B11" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>131130696</v>
       </c>
       <c r="B12" t="n">
-        <v>91818</v>
+        <v>91821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>131130718</v>
       </c>
       <c r="B14" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131295721</v>
       </c>
       <c r="B15" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -1214,7 +1214,7 @@
         <v>131129770</v>
       </c>
       <c r="B7" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>131130868</v>
       </c>
       <c r="B8" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1428,7 +1428,7 @@
         <v>131130889</v>
       </c>
       <c r="B9" t="n">
-        <v>58528</v>
+        <v>58529</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>131129861</v>
       </c>
       <c r="B10" t="n">
-        <v>58528</v>
+        <v>58529</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1649,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131131304</v>
+        <v>131130696</v>
       </c>
       <c r="B11" t="n">
-        <v>91841</v>
+        <v>91822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1660,19 +1660,23 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1680,10 +1684,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410603</v>
+        <v>410606</v>
       </c>
       <c r="R11" t="n">
-        <v>7037541</v>
+        <v>7037656</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1719,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1725,7 +1729,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,10 +1756,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130696</v>
+        <v>131131304</v>
       </c>
       <c r="B12" t="n">
-        <v>91821</v>
+        <v>91842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1763,23 +1767,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1787,10 +1787,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410606</v>
+        <v>410603</v>
       </c>
       <c r="R12" t="n">
-        <v>7037656</v>
+        <v>7037541</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,7 +1862,7 @@
         <v>131130472</v>
       </c>
       <c r="B13" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>131130718</v>
       </c>
       <c r="B14" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2076,7 +2076,7 @@
         <v>131295721</v>
       </c>
       <c r="B15" t="n">
-        <v>91841</v>
+        <v>91842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130961918</v>
+        <v>131130696</v>
       </c>
       <c r="B2" t="n">
-        <v>91833</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -706,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410588</v>
+        <v>410606</v>
       </c>
       <c r="R2" t="n">
-        <v>7037536</v>
+        <v>7037656</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -736,29 +740,29 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -778,27 +782,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130962101</v>
+        <v>131130718</v>
       </c>
       <c r="B3" t="n">
-        <v>58521</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102125</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -807,21 +811,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410575</v>
+        <v>410608</v>
       </c>
       <c r="R3" t="n">
-        <v>7037535</v>
+        <v>7037661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +892,7 @@
         <v>130961957</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +999,7 @@
         <v>130962220</v>
       </c>
       <c r="B5" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1106,7 @@
         <v>131076706</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131129770</v>
+        <v>131077474</v>
       </c>
       <c r="B7" t="n">
-        <v>57897</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410609</v>
+        <v>410575</v>
       </c>
       <c r="R7" t="n">
-        <v>7037521</v>
+        <v>7037632</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,22 +1275,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131130868</v>
+        <v>131129770</v>
       </c>
       <c r="B8" t="n">
-        <v>57897</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410593</v>
+        <v>410609</v>
       </c>
       <c r="R8" t="n">
-        <v>7037644</v>
+        <v>7037521</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,22 +1382,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,27 +1424,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131130889</v>
+        <v>131130472</v>
       </c>
       <c r="B9" t="n">
-        <v>58534</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1454,21 +1453,16 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>410590</v>
+        <v>410737</v>
       </c>
       <c r="R9" t="n">
-        <v>7037649</v>
+        <v>7037762</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,22 +1489,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1537,27 +1531,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131129861</v>
+        <v>131130868</v>
       </c>
       <c r="B10" t="n">
-        <v>58534</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102125</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1566,21 +1560,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410588</v>
+        <v>410593</v>
       </c>
       <c r="R10" t="n">
-        <v>7037509</v>
+        <v>7037644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,22 +1596,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,41 +1638,50 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131131304</v>
+        <v>130962101</v>
       </c>
       <c r="B11" t="n">
-        <v>91847</v>
+        <v>58592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>102125</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Pinicola enucleator</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410603</v>
+        <v>410575</v>
       </c>
       <c r="R11" t="n">
-        <v>7037541</v>
+        <v>7037535</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,22 +1708,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1752,45 +1750,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131130696</v>
+        <v>131129861</v>
       </c>
       <c r="B12" t="n">
-        <v>91827</v>
+        <v>58592</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>102125</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410606</v>
+        <v>410588</v>
       </c>
       <c r="R12" t="n">
-        <v>7037656</v>
+        <v>7037509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1832,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1859,27 +1862,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131130472</v>
+        <v>131130889</v>
       </c>
       <c r="B13" t="n">
-        <v>57897</v>
+        <v>58592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102125</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1888,16 +1891,21 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410737</v>
+        <v>410590</v>
       </c>
       <c r="R13" t="n">
-        <v>7037762</v>
+        <v>7037649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,22 +1932,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1963,216 +1971,6 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>131130718</v>
-      </c>
-      <c r="B14" t="n">
-        <v>57894</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>410608</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7037661</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:36</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>131295721</v>
-      </c>
-      <c r="B15" t="n">
-        <v>91858</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Stor-Grundsviken, Stor-Grundsviken, Jmt</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>410530</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7037500</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Åre</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Kall</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:44</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Fabian Pettersson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62545-2025 artfynd.xlsx
+++ b/artfynd/A 62545-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131130696</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131130718</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130961957</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962220</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131076706</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131077474</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131129770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131130472</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131130868</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130962101</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1859,6 +1914,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131129861</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1971,8 +2031,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131130889</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>